--- a/artfynd/A 20980-2024 artfynd.xlsx
+++ b/artfynd/A 20980-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86306884</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
+        <v>98116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424623.9271445697</v>
+        <v>424624</v>
       </c>
       <c r="R2" t="n">
-        <v>6477137.798594807</v>
+        <v>6477138</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +748,9 @@
           <t>2020-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1033,7 +1023,7 @@
         <v>87137328</v>
       </c>
       <c r="B5" t="n">
-        <v>100515</v>
+        <v>102304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424604.7877496492</v>
+        <v>424605</v>
       </c>
       <c r="R5" t="n">
-        <v>6477179.545634206</v>
+        <v>6477180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1093,9 @@
           <t>2020-07-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1154,7 +1134,7 @@
         <v>97352519</v>
       </c>
       <c r="B6" t="n">
-        <v>96356</v>
+        <v>98102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424593.3260959751</v>
+        <v>424593</v>
       </c>
       <c r="R6" t="n">
-        <v>6477211.192979348</v>
+        <v>6477211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,19 +1204,9 @@
           <t>2008-08-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-08-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1245,7 @@
         <v>101010623</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424499.7299096363</v>
+        <v>424500</v>
       </c>
       <c r="R7" t="n">
-        <v>6477283.178210291</v>
+        <v>6477283</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,19 +1320,9 @@
           <t>2022-05-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 20980-2024 artfynd.xlsx
+++ b/artfynd/A 20980-2024 artfynd.xlsx
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 20980-2024 artfynd.xlsx
+++ b/artfynd/A 20980-2024 artfynd.xlsx
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
